--- a/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
+++ b/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
@@ -31,10 +31,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -101,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -129,11 +130,12 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -505,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -542,7 +544,7 @@
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>THREE CLASSES OF CELL ARE PASTED, AND ONLY THREE.</t>
+          <t>FOUR CLASSES OF CELL ARE PASTED, AND ONLY FOUR.</t>
         </is>
       </c>
     </row>
@@ -563,49 +565,56 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. The sensitivity grids. Each cell there is a complete re-run of the whole model, including the unit build, so it cannot be a single formula. Those grids do NOT redraw when a driver is changed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="14" customHeight="1">
+          <t xml:space="preserve">  3. The sensitivity grids. Each cell there is a complete re-run of the whole model with joint driver shifts, so it cannot be a single formula. Those grids do NOT redraw when a driver is changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  4. Two whole-model re-runs named individually: the bear and bull of the cash-flow lens on the Summary sheet, whose joint driver sets (margin plus or minus 1.5 points, cost of capital minus or plus 1.5 points, terminal growth 2% or 4%, like-for-like plus or minus 1 point) are stated beside them; and the leases-as-operating-cost reading on the Fundamental Valuation sheet. The expert panel, both readings of the margin question, the cyclical value and every lens bear and bull are LIVE FORMULAS in this edition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Anything else pasted would be a defect. The formula and pasted-value counts are reported at the foot of this sheet.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="91" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15" ht="91" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>HOW REVENUE IS BUILT. Not as one growth rate. The restaurant estate is disclosed country by country at each period end and segment revenue is disclosed for the same units, so revenue is built as restaurants times revenue per restaurant across seven market units. The restaurant count grows on the company's own net-new-store guidance; the revenue per restaurant grows on disclosed like-for-like sales growth, less a currency drag applied only to the two markets whose currencies are not pegged to the dollar. The build reproduces reported revenue exactly in all three audited years. Margins are an OUTPUT of the cost stack, not an input: eight cost classes are each escalated on their own driver, never on one blended index.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>CURRENCY. The company reports in US dollars. The shares trade in dirhams in Abu Dhabi and in riyals in Riyadh, and the dirham has been pegged at 3.6725 to the dollar since 1997. The model runs in US dollars — the reporting and functional currency — and converts to dirhams at the peg. Figures are USD million unless stated; per-share figures are shown in both currencies.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>THE OPEN QUESTION. Between the first half of 2025 and the first half of 2026 the EBITDA margin went from 22.6% to 25.5%. Whether that is structural or cyclical is the single judgement that decides this valuation, and nothing in the filings settles it. Both readings are computed and both are published, on the Summary and Fundamental Valuation sheets. They are not averaged.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>WHAT IT IS NOT. It is not investment advice, a recommendation, or a price target. Values are model outputs shown as ranges.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>COUNTS. This workbook carries 779 formula cells against 385 pasted values — 275 audited or disclosed history, 40 engine outputs, and 70 sensitivity-grid cells. Every one of the 779 formula cells is checked against the model that wrote it.</t>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>COUNTS. This workbook carries 897 formula cells against 406 pasted values — 307 audited or disclosed history, 29 engine outputs, and 70 sensitivity-grid cells. Every one of the 897 formula cells is checked against the model that wrote it.</t>
         </is>
       </c>
     </row>
@@ -1110,35 +1119,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="26">
         <f>B17/'Income Statement'!B8</f>
         <v/>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>C17/'Income Statement'!C8</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <f>D17/'Income Statement'!D8</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>E17/'Income Statement'!E8</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>F17/'Income Statement'!F8</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="26">
         <f>G17/'Income Statement'!G8</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="26">
         <f>H17/'Income Statement'!H8</f>
         <v/>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="26">
         <f>I17/'Income Statement'!I8</f>
         <v/>
       </c>
@@ -1392,23 +1401,23 @@
           <t>Gross openings — net additions plus closures</t>
         </is>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="19">
         <f>Assumptions!B$11+Segments!C12*Assumptions!$C$63</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="19">
         <f>Assumptions!C$11+Segments!D12*Assumptions!$C$63</f>
         <v/>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="19">
         <f>Assumptions!D$11+Segments!E12*Assumptions!$C$63</f>
         <v/>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="19">
         <f>Assumptions!E$11+Segments!F12*Assumptions!$C$63</f>
         <v/>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="19">
         <f>Assumptions!F$11+Segments!G12*Assumptions!$C$63</f>
         <v/>
       </c>
@@ -1954,7 +1963,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>EBIT (before impairments in the forecast)</t>
         </is>
       </c>
       <c r="B8" s="10">
@@ -2074,7 +2083,7 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2114,17 +2123,17 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2156,17 +2165,17 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2198,17 +2207,17 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2329,7 +2338,7 @@
       <c r="F5" s="9" t="n">
         <v>2.60694021209324</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="21" t="n">
         <v>0.49858</v>
       </c>
     </row>
@@ -2354,7 +2363,7 @@
       <c r="F6" s="9" t="n">
         <v>2.960271871748596</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>0.50078</v>
       </c>
     </row>
@@ -2381,10 +2390,10 @@
           <t>Finishes 10% or more above the market price</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.15014</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <v>0.27504</v>
       </c>
     </row>
@@ -2394,10 +2403,10 @@
           <t>Finishes 10% or more below the market price</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>0.128</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <v>0.25438</v>
       </c>
     </row>
@@ -2407,10 +2416,10 @@
           <t>Touches 10% above at any point</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>0.24976</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.50802</v>
       </c>
     </row>
@@ -2420,10 +2429,10 @@
           <t>Touches 10% below at any point</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>0.21174</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>0.46714</v>
       </c>
     </row>
@@ -2445,7 +2454,7 @@
           <t>Simulated paths</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="20" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2455,7 +2464,7 @@
           <t>Anchor date</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -2477,7 +2486,7 @@
           <t>Annualised volatility at the anchor</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="21" t="n">
         <v>0.3561719340771033</v>
       </c>
     </row>
@@ -2487,7 +2496,7 @@
           <t>Dividend yield inside the drift anchor</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="21" t="n">
         <v>0.03952466367713004</v>
       </c>
     </row>
@@ -2566,111 +2575,111 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>8.10%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2.983957897448409</v>
+        <v>2.689963203325789</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>3.193895506271109</v>
+        <v>2.860337885054136</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3.446036846123456</v>
+        <v>3.064248697728378</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3.754530363281737</v>
+        <v>3.312848422877485</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>4.140644320591062</v>
+        <v>3.622851685899725</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>8.85%</t>
+          <t>8.75%</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>2.627257899649083</v>
+        <v>2.362314109361936</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2.784672955202872</v>
+        <v>2.488118720415106</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.969587044118522</v>
+        <v>2.635369723229186</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3.189895554967672</v>
+        <v>2.810182471952523</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3.456836274743236</v>
+        <v>3.021241547941936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>9.60%</t>
+          <t>9.50%</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>2.342506518084509</v>
+        <v>2.100325927119413</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2.463810245778002</v>
+        <v>2.195715870481494</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2.603849919309895</v>
+        <v>2.305421681630923</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2.767329607552111</v>
+        <v>2.433016097897558</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2.960671953728295</v>
+        <v>2.583368567260923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>10.35%</t>
+          <t>10.25%</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>2.110007227493929</v>
+        <v>1.886105952820147</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2.205557186216927</v>
+        <v>1.959982266853094</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.314333178438904</v>
+        <v>2.043742616089398</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2.439285518588842</v>
+        <v>2.13958005375153</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.584312506930077</v>
+        <v>2.250388237346297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>11.10%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1.916648315334795</v>
+        <v>1.707719127700286</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1.993279882146034</v>
+        <v>1.765930588738839</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2.079521163850661</v>
+        <v>1.831153911590974</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2.177300689984884</v>
+        <v>1.90478951514285</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2.28910002222223</v>
+        <v>1.988637340851779</v>
       </c>
     </row>
     <row r="12">
@@ -2710,111 +2719,111 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>8.10%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>2.963309887659626</v>
+        <v>2.596476620793644</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>3.20467336689154</v>
+        <v>2.83036265926101</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3.446036846123456</v>
+        <v>3.064248697728378</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>3.687400325355372</v>
+        <v>3.298134736195744</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.928763804587287</v>
+        <v>3.532020774663111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>8.85%</t>
+          <t>8.75%</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>2.551041087432431</v>
+        <v>2.22829044897828</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2.760314065775476</v>
+        <v>2.431830086103732</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2.969587044118522</v>
+        <v>2.635369723229186</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3.178860022461569</v>
+        <v>2.838909360354638</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.388133000804614</v>
+        <v>3.04244899748009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>9.60%</t>
+          <t>9.50%</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>2.234593124566388</v>
+        <v>1.945071282019615</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2.419221521938141</v>
+        <v>2.125246481825268</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.603849919309895</v>
+        <v>2.305421681630923</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2.78847831668165</v>
+        <v>2.485596881436576</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2.973106714053403</v>
+        <v>2.665772081242229</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>10.35%</t>
+          <t>10.25%</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>1.984112399074776</v>
+        <v>1.720483475001578</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>2.14922278875684</v>
+        <v>1.882113045545488</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2.314333178438904</v>
+        <v>2.043742616089398</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2.479443568120968</v>
+        <v>2.205372186633307</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2.644553957803032</v>
+        <v>2.367001757177217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>11.10%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>1.780976821909304</v>
+        <v>1.538054535967304</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1.930248992879982</v>
+        <v>1.684604223779139</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2.079521163850661</v>
+        <v>1.831153911590974</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2.22879333482134</v>
+        <v>1.977703599402809</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2.378065505792018</v>
+        <v>2.124253287214644</v>
       </c>
     </row>
     <row r="20">
@@ -2836,19 +2845,19 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2.439970289008469</v>
+        <v>2.15658397818916</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2.521093270213644</v>
+        <v>2.230264896942197</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.603849919309895</v>
+        <v>2.305421681630923</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2.688264647528674</v>
+        <v>2.38207632785189</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2.774362106745425</v>
+        <v>2.460251047727809</v>
       </c>
       <c r="H21" s="12">
         <f>MAX(B21:F21)-MIN(B21:F21)</f>
@@ -2862,19 +2871,19 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>2.234593124566388</v>
+        <v>1.945071282019615</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2.419221521938141</v>
+        <v>2.125246481825268</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.603849919309895</v>
+        <v>2.305421681630923</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2.78847831668165</v>
+        <v>2.485596881436576</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2.973106714053403</v>
+        <v>2.665772081242229</v>
       </c>
       <c r="H22" s="12">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2888,19 +2897,19 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>3.446036846123456</v>
+        <v>3.064248697728378</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>2.969587044118522</v>
+        <v>2.635369723229186</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2.603849919309895</v>
+        <v>2.305421681630923</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2.314333178438904</v>
+        <v>2.043742616089398</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2.079521163850661</v>
+        <v>1.831153911590974</v>
       </c>
       <c r="H23" s="12">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2914,19 +2923,19 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2.342506518084509</v>
+        <v>2.100325927119413</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2.463810245778002</v>
+        <v>2.195715870481494</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.603849919309895</v>
+        <v>2.305421681630923</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2.767329607552111</v>
+        <v>2.433016097897558</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2.960671953728295</v>
+        <v>2.583368567260923</v>
       </c>
       <c r="H24" s="12">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -3032,35 +3041,35 @@
           <t>Earnings per share (USD)</t>
         </is>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>'Income Statement'!B20</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>'Income Statement'!C20</f>
         <v/>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <f>'Income Statement'!D20</f>
         <v/>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <f>'Income Statement'!E20</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <f>'Income Statement'!F20</f>
         <v/>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="25">
         <f>'Income Statement'!G20</f>
         <v/>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="25">
         <f>'Income Statement'!H20</f>
         <v/>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="25">
         <f>'Income Statement'!I20</f>
         <v/>
       </c>
@@ -3071,35 +3080,35 @@
           <t>Earnings per share (AED)</t>
         </is>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <f>B5*Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>C5*Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>D5*Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>E5*Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>F5*Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <f>G5*Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="27">
         <f>H5*Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="27">
         <f>I5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -3110,35 +3119,35 @@
           <t>Book value per share (USD)</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <f>'Balance Sheet'!B14/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>'Balance Sheet'!C14/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>'Balance Sheet'!D14/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>'Balance Sheet'!E14/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>'Balance Sheet'!F14/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>'Balance Sheet'!G14/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <f>'Balance Sheet'!H14/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>'Balance Sheet'!I14/Assumptions!$C$7</f>
         <v/>
       </c>
@@ -3266,17 +3275,17 @@
           <t>Revenue per restaurant (USD thousand)</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3308,17 +3317,17 @@
           <t>Restaurants at year end</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3350,7 +3359,7 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3390,17 +3399,17 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3549,35 +3558,35 @@
           <t>Dividend per share (USD)</t>
         </is>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <f>'Cash Flow'!B17/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <f>'Cash Flow'!C17/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>'Cash Flow'!D17/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>'Cash Flow'!E17/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <f>'Cash Flow'!F17/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="27">
         <f>'Cash Flow'!G17/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="27">
         <f>'Cash Flow'!H17/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="27">
         <f>'Cash Flow'!I17/Assumptions!$C$7</f>
         <v/>
       </c>
@@ -3661,15 +3670,15 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <v>115.53</v>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="21" t="n">
         <v>0.02580007029324133</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -3689,15 +3698,15 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>17.61</v>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>0.07562763268564159</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -3717,13 +3726,13 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>11.25</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>23.08</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>0.1214890405680459</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -3743,13 +3752,13 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>6.02</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>16.43</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>0.1529514116662708</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -3769,13 +3778,13 @@
           <t>India</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>23.05</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>85.5</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>0.1454268733251085</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -3795,15 +3804,15 @@
           <t>India</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>33.28</v>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <v>0.1044915212476157</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -3823,15 +3832,15 @@
           <t>India</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>27.59</v>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>0.09488411880116998</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -3851,13 +3860,13 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>17.56</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>18.96</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>0.3517541899821757</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -3877,13 +3886,13 @@
           <t>China</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>17.48</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <v>0.1510693135560875</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -3903,13 +3912,13 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>14.32</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>18.57</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>0.3014743688553667</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -3929,13 +3938,13 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>16.19</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <v>19.88</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="21" t="n">
         <v>0.2035703385892659</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -3947,21 +3956,23 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Peer median, enterprise value / EBITDA (usable comparators)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>16.87</v>
+          <t>Peer median, enterprise value / EBITDA — MEDIAN over the rows inside the stated band of 4x to 40x (one exclusion: the row whose multiple is an arithmetic artefact of a depressed year)</t>
+        </is>
+      </c>
+      <c r="C17" s="26">
+        <f>MEDIAN(C6,C7,C8,C9,C10,C11,C12,C13,C14,C15)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Peer median, price / earnings (usable comparators)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>18.76</v>
+          <t>Peer median, price / earnings — MEDIAN over the rows inside the stated band of 5x to 45x</t>
+        </is>
+      </c>
+      <c r="D18" s="26">
+        <f>MEDIAN(D7,D8,D12,D13,D14,D15)</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -4091,14 +4102,14 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>1.603537665804741</v>
+        <v>1.400021011084784</v>
       </c>
       <c r="C5" s="10">
         <f>DCF!C39</f>
         <v/>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4.88152606537727</v>
+        <v>4.29768913036704</v>
       </c>
       <c r="E5" s="11">
         <f>Assumptions!$C$103</f>
@@ -4123,15 +4134,17 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>1.993757665534047</v>
+      <c r="B6" s="10">
+        <f>'Relative &amp; Normalized'!C13</f>
+        <v/>
       </c>
       <c r="C6" s="10">
         <f>'Relative &amp; Normalized'!B12</f>
         <v/>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>2.974725744874325</v>
+      <c r="D6" s="10">
+        <f>'Relative &amp; Normalized'!D13</f>
+        <v/>
       </c>
       <c r="E6" s="11">
         <f>Assumptions!$C$104</f>
@@ -4152,15 +4165,17 @@
           <t>Normalised earnings power</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>1.773604583718904</v>
+      <c r="B7" s="10">
+        <f>'Relative &amp; Normalized'!C32</f>
+        <v/>
       </c>
       <c r="C7" s="10">
         <f>'Relative &amp; Normalized'!B31</f>
         <v/>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>2.865053558315152</v>
+      <c r="D7" s="10">
+        <f>'Relative &amp; Normalized'!D32</f>
+        <v/>
       </c>
       <c r="E7" s="11">
         <f>Assumptions!$C$105</f>
@@ -4181,15 +4196,17 @@
           <t>Book value and sustainable return</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>0.6589204333152275</v>
+      <c r="B8" s="10">
+        <f>'Relative &amp; Normalized'!C41</f>
+        <v/>
       </c>
       <c r="C8" s="10">
         <f>'Relative &amp; Normalized'!B40</f>
         <v/>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>1.43862989576031</v>
+      <c r="D8" s="10">
+        <f>'Relative &amp; Normalized'!D41</f>
+        <v/>
       </c>
       <c r="E8" s="11">
         <f>Assumptions!$C$106</f>
@@ -4207,11 +4224,11 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Weighted central</t>
+          <t>Weighted central — outer columns are the weighted bear and bull</t>
         </is>
       </c>
       <c r="B10" s="12">
-        <f>MIN(B5:B8)</f>
+        <f>B5*E5+B6*E6+B7*E7+B8*E8</f>
         <v/>
       </c>
       <c r="C10" s="12">
@@ -4219,7 +4236,7 @@
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>MAX(D5:D8)</f>
+        <f>D5*E5+D6*E6+D7*E7+D8*E8</f>
         <v/>
       </c>
       <c r="E10" s="13">
@@ -4234,15 +4251,15 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Expert panel median</t>
-        </is>
-      </c>
-      <c r="C11" s="10">
-        <f>'Fundamental Valuation'!C29</f>
-        <v/>
-      </c>
-      <c r="H11" s="13">
-        <f>C11/$C$12-1</f>
+          <t>Range across the lenses (widest bear to widest bull, unweighted)</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>MIN(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="D11" s="12">
+        <f>MAX(D5:D8)</f>
         <v/>
       </c>
     </row>
@@ -4257,6 +4274,21 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Expert panel median</t>
+        </is>
+      </c>
+      <c r="C13" s="10">
+        <f>'Fundamental Valuation'!C29</f>
+        <v/>
+      </c>
+      <c r="H13" s="13">
+        <f>C13/$C$12-1</f>
+        <v/>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -4370,7 +4402,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Restaurants at 30 June 2026</t>
+          <t>Restaurants at 31 December 2025</t>
         </is>
       </c>
       <c r="C25" s="15">
@@ -4440,7 +4472,7 @@
         </is>
       </c>
       <c r="C31" s="11">
-        <f>201.6/DCF!C56</f>
+        <f>Assumptions!$C$126/DCF!C56</f>
         <v/>
       </c>
     </row>
@@ -4586,11 +4618,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>The base case. Food and packaging stays near the 27.4% of revenue the company actually recorded in the first half of 2026, and the EBITDA margin runs from 25.3% to 26.1% across the forecast.</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>2.603849919309895</v>
+          <t>The base case. Food and packaging stays near the 27.4% of revenue the company actually recorded in the first half of 2026, and the EBITDA margin runs from 25.4% to a peak of 25.4% before the growing delivery channel eases it to 24.9%.</t>
+        </is>
+      </c>
+      <c r="C13" s="10">
+        <f>DCF!C39</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -4604,8 +4637,9 @@
           <t>The first half of 2026 is banked, and the EBITDA margin then reverts in a straight line to the three-year audited average of 22.8% by FY2030.</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
-        <v>2.063858519339359</v>
+      <c r="C14" s="10">
+        <f>DCF!C79</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -4622,7 +4656,7 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Both are complete re-runs of the whole model, including the unit build, so they are engine outputs rather than formulas. They are published side by side and never averaged.</t>
+          <t>Both readings are LIVE in this workbook: the structural value is the DCF sheet headline and the cyclical value is the parallel formula block at the foot of the DCF sheet, sharing every driver except the margin path. They are published side by side and never averaged.</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4674,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2.603849919309895</v>
+        <v>2.305421681630923</v>
       </c>
     </row>
     <row r="20">
@@ -4650,7 +4684,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2.553946563069939</v>
+        <v>2.259144982128687</v>
       </c>
     </row>
     <row r="21">
@@ -4716,14 +4750,17 @@
           <t>Restaurant-level unit economics</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
-        <v>2.046500790489335</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>1.750615103834287</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>2.314696696510654</v>
+      <c r="C26" s="12">
+        <f>(((2*Assumptions!$C$124-Assumptions!$C$125-Assumptions!$C$62*DCF!B5-Assumptions!$C$65*DCF!B5)*(1-Assumptions!$C$71)/DCF!C61+Assumptions!$C$88-Assumptions!$C$90)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D26" s="12">
+        <f>(((2*Assumptions!$C$124-Assumptions!$C$125-Assumptions!$C$62*DCF!B5-Assumptions!$C$65*DCF!B5)*(1-Assumptions!$C$71)/(DCF!C61+0.015)+Assumptions!$C$88-Assumptions!$C$90)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E26" s="12">
+        <f>(((2*Assumptions!$C$124-Assumptions!$C$125-Assumptions!$C$62*DCF!B5-Assumptions!$C$65*DCF!B5)*(1-Assumptions!$C$71)/(DCF!C61-0.01)+Assumptions!$C$88-Assumptions!$C$90)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -4737,14 +4774,17 @@
           <t>Distributable cash as a perpetuity</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
-        <v>1.306146726080504</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>1.004476914796291</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>1.681696866321748</v>
+      <c r="C27" s="12">
+        <f>(Assumptions!$C$126/Assumptions!$C$7*(1+Assumptions!$C$84)/(DCF!C61-Assumptions!$C$84)*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D27" s="12">
+        <f>(Assumptions!$C$126/Assumptions!$C$7*1.02/(DCF!C61+0.01-0.02)*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E27" s="12">
+        <f>(Assumptions!$C$126/Assumptions!$C$7*1.04/(DCF!C61-0.005-0.04)*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -4758,14 +4798,17 @@
           <t>Return on capital against the cost of capital</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n">
-        <v>1.926947999420108</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>1.250851561624927</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>2.291196528979463</v>
+      <c r="C28" s="12">
+        <f>((DCF!B12/DCF!C53+DCF!B12*(DCF!B12/'Balance Sheet'!E18-DCF!C53)/(DCF!B12/'Balance Sheet'!E18)*Assumptions!$C$84/(DCF!C53*(DCF!C53-Assumptions!$C$84))+DCF!C33+DCF!C34+DCF!C35+DCF!C36)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D28" s="12">
+        <f>((DCF!B12/(DCF!C53+0.01)+DCF!C33+DCF!C34+DCF!C35+DCF!C36)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E28" s="12">
+        <f>(((DCF!B12/DCF!C53+DCF!B12*(DCF!B12/'Balance Sheet'!E18-DCF!C53)/(DCF!B12/'Balance Sheet'!E18)*Assumptions!$C$84/(DCF!C53*(DCF!C53-Assumptions!$C$84)))*1.18+DCF!C33+DCF!C34+DCF!C35+DCF!C36)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -4790,7 +4833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4877,11 +4920,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Shares outstanding, net of treasury (million)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>8398.633099999999</v>
+          <t>Shares outstanding, net of treasury (million) — issued less treasury</t>
+        </is>
+      </c>
+      <c r="C7" s="19">
+        <f>C8-E8</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -4890,8 +4934,16 @@
           <t>Shares issued (million)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>8423.633099999999</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>less treasury (million)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -4907,19 +4959,19 @@
           <t>Net new restaurants a year</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="20" t="n">
         <v>125</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>125</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4936,7 +4988,7 @@
           <t xml:space="preserve">   UAE</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="21" t="n">
         <v>0.26</v>
       </c>
     </row>
@@ -4946,7 +4998,7 @@
           <t xml:space="preserve">   Saudi Arabia</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="21" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4956,7 +5008,7 @@
           <t xml:space="preserve">   Kuwait</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="21" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4966,7 +5018,7 @@
           <t xml:space="preserve">   Egypt</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="21" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -4976,7 +5028,7 @@
           <t xml:space="preserve">   Morocco</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="21" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -4986,7 +5038,7 @@
           <t xml:space="preserve">   Lower Gulf</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4996,7 +5048,7 @@
           <t xml:space="preserve">   Other markets</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="21" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5013,7 +5065,7 @@
           <t xml:space="preserve">   UAE</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="20" t="n">
         <v>652</v>
       </c>
     </row>
@@ -5023,7 +5075,7 @@
           <t xml:space="preserve">   Saudi Arabia</t>
         </is>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="20" t="n">
         <v>766</v>
       </c>
     </row>
@@ -5033,7 +5085,7 @@
           <t xml:space="preserve">   Kuwait</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="20" t="n">
         <v>276</v>
       </c>
     </row>
@@ -5043,7 +5095,7 @@
           <t xml:space="preserve">   Egypt</t>
         </is>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="20" t="n">
         <v>450</v>
       </c>
     </row>
@@ -5053,7 +5105,7 @@
           <t xml:space="preserve">   Morocco</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="20" t="n">
         <v>55</v>
       </c>
     </row>
@@ -5063,7 +5115,7 @@
           <t xml:space="preserve">   Lower Gulf</t>
         </is>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="20" t="n">
         <v>287</v>
       </c>
     </row>
@@ -5073,7 +5125,7 @@
           <t xml:space="preserve">   Other markets</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="20" t="n">
         <v>263</v>
       </c>
     </row>
@@ -5090,19 +5142,19 @@
           <t>Like-for-like sales growth</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="21" t="n">
         <v>0.055</v>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="21" t="n">
         <v>0.045</v>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="21" t="n">
         <v>0.04</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="21" t="n">
         <v>0.037</v>
       </c>
-      <c r="F30" s="20" t="n">
+      <c r="F30" s="21" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -5119,7 +5171,7 @@
           <t xml:space="preserve">   UAE</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5129,7 +5181,7 @@
           <t xml:space="preserve">   Saudi Arabia</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5139,7 +5191,7 @@
           <t xml:space="preserve">   Kuwait</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5149,7 +5201,7 @@
           <t xml:space="preserve">   Egypt</t>
         </is>
       </c>
-      <c r="C35" s="20" t="n">
+      <c r="C35" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -5159,7 +5211,7 @@
           <t xml:space="preserve">   Morocco</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="21" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -5169,7 +5221,7 @@
           <t xml:space="preserve">   Lower Gulf</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5179,7 +5231,7 @@
           <t xml:space="preserve">   Other markets</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="21" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -5273,19 +5325,19 @@
           <t>Food, filling and packing materials</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n">
+      <c r="B49" s="22" t="n">
         <v>0.274</v>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C49" s="22" t="n">
         <v>0.2725</v>
       </c>
-      <c r="D49" s="21" t="n">
+      <c r="D49" s="22" t="n">
         <v>0.2715</v>
       </c>
-      <c r="E49" s="21" t="n">
+      <c r="E49" s="22" t="n">
         <v>0.271</v>
       </c>
-      <c r="F49" s="21" t="n">
+      <c r="F49" s="22" t="n">
         <v>0.2705</v>
       </c>
     </row>
@@ -5295,64 +5347,34 @@
           <t>Royalties to the brand franchisors</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n">
+      <c r="B50" s="22" t="n">
         <v>0.0555</v>
       </c>
-      <c r="C50" s="21" t="n">
+      <c r="C50" s="22" t="n">
         <v>0.0555</v>
       </c>
-      <c r="D50" s="21" t="n">
+      <c r="D50" s="22" t="n">
         <v>0.0555</v>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="E50" s="22" t="n">
         <v>0.0555</v>
       </c>
-      <c r="F50" s="21" t="n">
+      <c r="F50" s="22" t="n">
         <v>0.0555</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Staff costs</t>
-        </is>
-      </c>
-      <c r="B51" s="21" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="C51" s="21" t="n">
-        <v>0.1805</v>
-      </c>
-      <c r="D51" s="21" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E51" s="21" t="n">
-        <v>0.1798</v>
-      </c>
-      <c r="F51" s="21" t="n">
-        <v>0.1795</v>
+          <t>Staff costs — UNIT BUILD, not a share: inputs at rows 109-114 below</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Home delivery and transportation</t>
-        </is>
-      </c>
-      <c r="B52" s="21" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>0.07149999999999999</v>
-      </c>
-      <c r="D52" s="21" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="E52" s="21" t="n">
-        <v>0.07049999999999999</v>
-      </c>
-      <c r="F52" s="21" t="n">
-        <v>0.07000000000000001</v>
+          <t>Home delivery and transportation — UNIT BUILD, not a share: inputs at rows 109-114 below</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -5361,19 +5383,19 @@
           <t>Advertisement and business development</t>
         </is>
       </c>
-      <c r="B53" s="21" t="n">
+      <c r="B53" s="22" t="n">
         <v>0.0425</v>
       </c>
-      <c r="C53" s="21" t="n">
+      <c r="C53" s="22" t="n">
         <v>0.0425</v>
       </c>
-      <c r="D53" s="21" t="n">
+      <c r="D53" s="22" t="n">
         <v>0.0425</v>
       </c>
-      <c r="E53" s="21" t="n">
+      <c r="E53" s="22" t="n">
         <v>0.0425</v>
       </c>
-      <c r="F53" s="21" t="n">
+      <c r="F53" s="22" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -5383,19 +5405,19 @@
           <t>Utilities and communication</t>
         </is>
       </c>
-      <c r="B54" s="21" t="n">
+      <c r="B54" s="22" t="n">
         <v>0.0283</v>
       </c>
-      <c r="C54" s="21" t="n">
+      <c r="C54" s="22" t="n">
         <v>0.0282</v>
       </c>
-      <c r="D54" s="21" t="n">
+      <c r="D54" s="22" t="n">
         <v>0.0281</v>
       </c>
-      <c r="E54" s="21" t="n">
+      <c r="E54" s="22" t="n">
         <v>0.028</v>
       </c>
-      <c r="F54" s="21" t="n">
+      <c r="F54" s="22" t="n">
         <v>0.0279</v>
       </c>
     </row>
@@ -5405,19 +5427,19 @@
           <t>Short-term, low-value and variable lease payments</t>
         </is>
       </c>
-      <c r="B55" s="21" t="n">
+      <c r="B55" s="22" t="n">
         <v>0.017</v>
       </c>
-      <c r="C55" s="21" t="n">
+      <c r="C55" s="22" t="n">
         <v>0.0169</v>
       </c>
-      <c r="D55" s="21" t="n">
+      <c r="D55" s="22" t="n">
         <v>0.0168</v>
       </c>
-      <c r="E55" s="21" t="n">
+      <c r="E55" s="22" t="n">
         <v>0.0167</v>
       </c>
-      <c r="F55" s="21" t="n">
+      <c r="F55" s="22" t="n">
         <v>0.0166</v>
       </c>
     </row>
@@ -5427,19 +5449,19 @@
           <t>Maintenance, repairs and other restaurant costs</t>
         </is>
       </c>
-      <c r="B56" s="21" t="n">
+      <c r="B56" s="22" t="n">
         <v>0.0288</v>
       </c>
-      <c r="C56" s="21" t="n">
+      <c r="C56" s="22" t="n">
         <v>0.0287</v>
       </c>
-      <c r="D56" s="21" t="n">
+      <c r="D56" s="22" t="n">
         <v>0.0286</v>
       </c>
-      <c r="E56" s="21" t="n">
+      <c r="E56" s="22" t="n">
         <v>0.0285</v>
       </c>
-      <c r="F56" s="21" t="n">
+      <c r="F56" s="22" t="n">
         <v>0.0284</v>
       </c>
     </row>
@@ -5449,7 +5471,7 @@
           <t>All other operating costs (the residual of the three expense notes)</t>
         </is>
       </c>
-      <c r="C57" s="21" t="n">
+      <c r="C57" s="22" t="n">
         <v>0.05313651312708256</v>
       </c>
     </row>
@@ -5459,7 +5481,7 @@
           <t>Other income, as a share of revenue</t>
         </is>
       </c>
-      <c r="C58" s="21" t="n">
+      <c r="C58" s="22" t="n">
         <v>0.005325609120778246</v>
       </c>
     </row>
@@ -5476,7 +5498,7 @@
           <t>Capital expenditure per new restaurant (USD thousand)</t>
         </is>
       </c>
-      <c r="C61" s="19" t="n">
+      <c r="C61" s="20" t="n">
         <v>402</v>
       </c>
     </row>
@@ -5486,7 +5508,7 @@
           <t>Maintenance capital expenditure, share of revenue</t>
         </is>
       </c>
-      <c r="C62" s="21" t="n">
+      <c r="C62" s="22" t="n">
         <v>0.01611753090395848</v>
       </c>
     </row>
@@ -5496,7 +5518,7 @@
           <t>Restaurant closure rate</t>
         </is>
       </c>
-      <c r="C63" s="21" t="n">
+      <c r="C63" s="22" t="n">
         <v>0.02073481265914878</v>
       </c>
     </row>
@@ -5506,7 +5528,7 @@
           <t>Additions to right-of-use assets, share of revenue</t>
         </is>
       </c>
-      <c r="C64" s="21" t="n">
+      <c r="C64" s="22" t="n">
         <v>0.08500000000000001</v>
       </c>
     </row>
@@ -5516,7 +5538,7 @@
           <t>Total lease payments, share of revenue</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n">
+      <c r="C65" s="22" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -5526,7 +5548,7 @@
           <t>Right-of-use depreciation rate, on the opening balance</t>
         </is>
       </c>
-      <c r="C66" s="21" t="n">
+      <c r="C66" s="22" t="n">
         <v>0.3631561653128501</v>
       </c>
     </row>
@@ -5536,7 +5558,7 @@
           <t>Owned-asset depreciation rate, on the opening balance</t>
         </is>
       </c>
-      <c r="C67" s="21" t="n">
+      <c r="C67" s="22" t="n">
         <v>0.2593798394144914</v>
       </c>
     </row>
@@ -5546,7 +5568,7 @@
           <t>Net working capital, share of revenue (negative — the till pays first)</t>
         </is>
       </c>
-      <c r="C68" s="21" t="n">
+      <c r="C68" s="22" t="n">
         <v>-0.09885719228274958</v>
       </c>
     </row>
@@ -5563,19 +5585,19 @@
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="B71" s="20" t="n">
+      <c r="B71" s="21" t="n">
         <v>0.145</v>
       </c>
-      <c r="C71" s="20" t="n">
+      <c r="C71" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="D71" s="20" t="n">
+      <c r="D71" s="21" t="n">
         <v>0.155</v>
       </c>
-      <c r="E71" s="20" t="n">
+      <c r="E71" s="21" t="n">
         <v>0.16</v>
       </c>
-      <c r="F71" s="20" t="n">
+      <c r="F71" s="21" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -5585,7 +5607,7 @@
           <t>Dividend payout ratio</t>
         </is>
       </c>
-      <c r="C72" s="20" t="n">
+      <c r="C72" s="21" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -5595,7 +5617,7 @@
           <t>Yield on cash and bank deposits</t>
         </is>
       </c>
-      <c r="C73" s="21" t="n">
+      <c r="C73" s="22" t="n">
         <v>0.04352664631793145</v>
       </c>
     </row>
@@ -5605,7 +5627,7 @@
           <t>Finance costs other than lease interest, share of revenue</t>
         </is>
       </c>
-      <c r="C74" s="21" t="n">
+      <c r="C74" s="22" t="n">
         <v>0.001302603892425965</v>
       </c>
     </row>
@@ -5622,8 +5644,8 @@
           <t>US ten-year Treasury yield</t>
         </is>
       </c>
-      <c r="C76" s="21" t="n">
-        <v>0.0466</v>
+      <c r="C76" s="22" t="n">
+        <v>0.0465</v>
       </c>
     </row>
     <row r="77">
@@ -5632,8 +5654,8 @@
           <t>US sovereign default spread (ratings basis)</t>
         </is>
       </c>
-      <c r="C77" s="21" t="n">
-        <v>0.0023</v>
+      <c r="C77" s="22" t="n">
+        <v>0.0022</v>
       </c>
     </row>
     <row r="78">
@@ -5642,8 +5664,8 @@
           <t>Blended equity risk premium (ratings basis)</t>
         </is>
       </c>
-      <c r="C78" s="21" t="n">
-        <v>0.06314712111898113</v>
+      <c r="C78" s="22" t="n">
+        <v>0.06200978170271963</v>
       </c>
     </row>
     <row r="79">
@@ -5652,8 +5674,8 @@
           <t>US sovereign credit-default-swap spread</t>
         </is>
       </c>
-      <c r="C79" s="21" t="n">
-        <v>0.003</v>
+      <c r="C79" s="22" t="n">
+        <v>0.0043</v>
       </c>
     </row>
     <row r="80">
@@ -5662,8 +5684,8 @@
           <t>Blended equity risk premium (credit-default-swap basis)</t>
         </is>
       </c>
-      <c r="C80" s="21" t="n">
-        <v>0.05949197635223904</v>
+      <c r="C80" s="22" t="n">
+        <v>0.05927625031955178</v>
       </c>
     </row>
     <row r="81">
@@ -5673,7 +5695,7 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>0.895</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="82">
@@ -5682,7 +5704,7 @@
           <t>Cost of debt — the group’s own incremental borrowing rate</t>
         </is>
       </c>
-      <c r="C82" s="21" t="n">
+      <c r="C82" s="22" t="n">
         <v>0.06719904760103823</v>
       </c>
     </row>
@@ -5692,8 +5714,8 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C83" s="21" t="n">
-        <v>0.043</v>
+      <c r="C83" s="22" t="n">
+        <v>0.0445</v>
       </c>
     </row>
     <row r="84">
@@ -5702,7 +5724,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C84" s="20" t="n">
+      <c r="C84" s="21" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -5799,7 +5821,7 @@
           <t>Intercompany eliminations, share of segment revenue</t>
         </is>
       </c>
-      <c r="C95" s="21" t="n">
+      <c r="C95" s="22" t="n">
         <v>0.01256442994650386</v>
       </c>
     </row>
@@ -5836,7 +5858,7 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C100" s="22" t="n">
+      <c r="C100" s="23" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -5846,7 +5868,7 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C101" s="22" t="n">
+      <c r="C101" s="23" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5856,7 +5878,7 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C102" s="20" t="n">
+      <c r="C102" s="21" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -5866,7 +5888,7 @@
           <t>Weight — discounted cash flow</t>
         </is>
       </c>
-      <c r="C103" s="20" t="n">
+      <c r="C103" s="21" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5876,7 +5898,7 @@
           <t>Weight — relative multiples</t>
         </is>
       </c>
-      <c r="C104" s="20" t="n">
+      <c r="C104" s="21" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5886,7 +5908,7 @@
           <t>Weight — normalised earnings power</t>
         </is>
       </c>
-      <c r="C105" s="20" t="n">
+      <c r="C105" s="21" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5896,8 +5918,203 @@
           <t>Weight — book value and sustainable return</t>
         </is>
       </c>
-      <c r="C106" s="20" t="n">
+      <c r="C106" s="21" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>Unit-built cost lines, the terminal fade, and the anchor roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>Restaurant-level staff per restaurant (full-time equivalents)</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>Staff cost per full-time equivalent (USD thousand, FY2025)</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="n">
+        <v>12.39331308624721</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>Wage growth per full-time equivalent</t>
+        </is>
+      </c>
+      <c r="C111" s="21" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>Above-restaurant staff (thousand full-time equivalents)</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="n">
+        <v>3.883</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>Home delivery share of revenue</t>
+        </is>
+      </c>
+      <c r="B113" s="21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C113" s="21" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="D113" s="21" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E113" s="21" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F113" s="21" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Delivery cost per dollar of delivered revenue</t>
+        </is>
+      </c>
+      <c r="B114" s="22" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="C114" s="22" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="D114" s="22" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>0.1405</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>Recurring impairment charge, share of revenue</t>
+        </is>
+      </c>
+      <c r="C115" s="22" t="n">
+        <v>0.003079211306099732</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>Terminal return on incremental invested capital</t>
+        </is>
+      </c>
+      <c r="C116" s="21" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>Calendar days, valuation date to the price anchor</t>
+        </is>
+      </c>
+      <c r="C117" s="20" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>Dividend paid inside the roll window (USD per share)</t>
+        </is>
+      </c>
+      <c r="C118" s="24" t="n">
+        <v>0.02400390606419038</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>Cyclical margin path (the other reading of the open question)</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="n">
+        <v>0.2539751872432852</v>
+      </c>
+      <c r="C119" s="21" t="n">
+        <v>0.2474672149418123</v>
+      </c>
+      <c r="D119" s="21" t="n">
+        <v>0.2409592426403394</v>
+      </c>
+      <c r="E119" s="21" t="n">
+        <v>0.2344512703388665</v>
+      </c>
+      <c r="F119" s="21" t="n">
+        <v>0.2279432980373936</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>Four-wall EBITDA, first half of 2026 (USD million)</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Corporate overhead for the owner-cash reading (USD million)</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="n">
+        <v>174.20332</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>Dividend declared against FY2025 (USD million)</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>201.6</v>
       </c>
     </row>
   </sheetData>
@@ -6110,7 +6327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6185,23 +6402,23 @@
         <f>Assumptions!$C$21</f>
         <v/>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="19">
         <f>B5+Assumptions!B$11*Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="19">
         <f>C5+Assumptions!C$11*Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="19">
         <f>D5+Assumptions!D$11*Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="19">
         <f>E5+Assumptions!E$11*Assumptions!$C$13</f>
         <v/>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="19">
         <f>F5+Assumptions!F$11*Assumptions!$C$13</f>
         <v/>
       </c>
@@ -6216,23 +6433,23 @@
         <f>Assumptions!$C$22</f>
         <v/>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="19">
         <f>B6+Assumptions!B$11*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="19">
         <f>C6+Assumptions!C$11*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="19">
         <f>D6+Assumptions!D$11*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="19">
         <f>E6+Assumptions!E$11*Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="19">
         <f>F6+Assumptions!F$11*Assumptions!$C$14</f>
         <v/>
       </c>
@@ -6247,23 +6464,23 @@
         <f>Assumptions!$C$23</f>
         <v/>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="19">
         <f>B7+Assumptions!B$11*Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="19">
         <f>C7+Assumptions!C$11*Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="19">
         <f>D7+Assumptions!D$11*Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="19">
         <f>E7+Assumptions!E$11*Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="19">
         <f>F7+Assumptions!F$11*Assumptions!$C$15</f>
         <v/>
       </c>
@@ -6278,23 +6495,23 @@
         <f>Assumptions!$C$24</f>
         <v/>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="19">
         <f>B8+Assumptions!B$11*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="19">
         <f>C8+Assumptions!C$11*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="19">
         <f>D8+Assumptions!D$11*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="19">
         <f>E8+Assumptions!E$11*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="19">
         <f>F8+Assumptions!F$11*Assumptions!$C$16</f>
         <v/>
       </c>
@@ -6309,23 +6526,23 @@
         <f>Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="19">
         <f>B9+Assumptions!B$11*Assumptions!$C$17</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="19">
         <f>C9+Assumptions!C$11*Assumptions!$C$17</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="19">
         <f>D9+Assumptions!D$11*Assumptions!$C$17</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="19">
         <f>E9+Assumptions!E$11*Assumptions!$C$17</f>
         <v/>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="19">
         <f>F9+Assumptions!F$11*Assumptions!$C$17</f>
         <v/>
       </c>
@@ -6340,23 +6557,23 @@
         <f>Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="19">
         <f>B10+Assumptions!B$11*Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="19">
         <f>C10+Assumptions!C$11*Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="19">
         <f>D10+Assumptions!D$11*Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="19">
         <f>E10+Assumptions!E$11*Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="19">
         <f>F10+Assumptions!F$11*Assumptions!$C$18</f>
         <v/>
       </c>
@@ -6371,23 +6588,23 @@
         <f>Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="19">
         <f>B11+Assumptions!B$11*Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="19">
         <f>C11+Assumptions!C$11*Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="19">
         <f>D11+Assumptions!D$11*Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="19">
         <f>E11+Assumptions!E$11*Assumptions!$C$19</f>
         <v/>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="19">
         <f>F11+Assumptions!F$11*Assumptions!$C$19</f>
         <v/>
       </c>
@@ -6398,27 +6615,27 @@
           <t>Total restaurants</t>
         </is>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="19">
         <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="19">
         <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="19">
         <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="19">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="19">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="19">
         <f>SUM(G5:G11)</f>
         <v/>
       </c>
@@ -7137,6 +7354,453 @@
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FY2026 is half disclosed and half built. The unit build and the first-half run rate are averaged rather than one being chosen over the other; the two are within two per cent of each other. The historical columns tie exactly to reported revenue in all three audited years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>THE BRAND BUILD — product by product, volume x price, the cross-check spine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Restaurants by brand</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>KFC</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>1089</v>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>1146</v>
+      </c>
+      <c r="D42" s="19">
+        <f>C42+Assumptions!B$11*0.4</f>
+        <v/>
+      </c>
+      <c r="E42" s="19">
+        <f>D42+Assumptions!C$11*0.4</f>
+        <v/>
+      </c>
+      <c r="F42" s="19">
+        <f>E42+Assumptions!D$11*0.4</f>
+        <v/>
+      </c>
+      <c r="G42" s="19">
+        <f>F42+Assumptions!E$11*0.4</f>
+        <v/>
+      </c>
+      <c r="H42" s="19">
+        <f>G42+Assumptions!F$11*0.4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Pizza Hut</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>432</v>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>457</v>
+      </c>
+      <c r="D43" s="19">
+        <f>C43+Assumptions!B$11*0.15</f>
+        <v/>
+      </c>
+      <c r="E43" s="19">
+        <f>D43+Assumptions!C$11*0.15</f>
+        <v/>
+      </c>
+      <c r="F43" s="19">
+        <f>E43+Assumptions!D$11*0.15</f>
+        <v/>
+      </c>
+      <c r="G43" s="19">
+        <f>F43+Assumptions!E$11*0.15</f>
+        <v/>
+      </c>
+      <c r="H43" s="19">
+        <f>G43+Assumptions!F$11*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Hardee's</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>410</v>
+      </c>
+      <c r="C44" s="20" t="n">
+        <v>458</v>
+      </c>
+      <c r="D44" s="19">
+        <f>C44+Assumptions!B$11*0.16</f>
+        <v/>
+      </c>
+      <c r="E44" s="19">
+        <f>D44+Assumptions!C$11*0.16</f>
+        <v/>
+      </c>
+      <c r="F44" s="19">
+        <f>E44+Assumptions!D$11*0.16</f>
+        <v/>
+      </c>
+      <c r="G44" s="19">
+        <f>F44+Assumptions!E$11*0.16</f>
+        <v/>
+      </c>
+      <c r="H44" s="19">
+        <f>G44+Assumptions!F$11*0.16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Krispy Kreme</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>388</v>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>395</v>
+      </c>
+      <c r="D45" s="19">
+        <f>C45+Assumptions!B$11*0.12</f>
+        <v/>
+      </c>
+      <c r="E45" s="19">
+        <f>D45+Assumptions!C$11*0.12</f>
+        <v/>
+      </c>
+      <c r="F45" s="19">
+        <f>E45+Assumptions!D$11*0.12</f>
+        <v/>
+      </c>
+      <c r="G45" s="19">
+        <f>F45+Assumptions!E$11*0.12</f>
+        <v/>
+      </c>
+      <c r="H45" s="19">
+        <f>G45+Assumptions!F$11*0.12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Growth, niche and other brands</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>271</v>
+      </c>
+      <c r="C46" s="20" t="n">
+        <v>293</v>
+      </c>
+      <c r="D46" s="19">
+        <f>C46+Assumptions!B$11*0.17</f>
+        <v/>
+      </c>
+      <c r="E46" s="19">
+        <f>D46+Assumptions!C$11*0.17</f>
+        <v/>
+      </c>
+      <c r="F46" s="19">
+        <f>E46+Assumptions!D$11*0.17</f>
+        <v/>
+      </c>
+      <c r="G46" s="19">
+        <f>F46+Assumptions!E$11*0.17</f>
+        <v/>
+      </c>
+      <c r="H46" s="19">
+        <f>G46+Assumptions!F$11*0.17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Revenue by brand (USD million; residual ties to the audited total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>KFC</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>1325</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>1494</v>
+      </c>
+      <c r="D49" s="12">
+        <f>D42*(C49/C42)*(1+Assumptions!B$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="E49" s="12">
+        <f>E42*(D49/D42)*(1+Assumptions!C$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="F49" s="12">
+        <f>F42*(E49/E42)*(1+Assumptions!D$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="G49" s="12">
+        <f>G42*(F49/F42)*(1+Assumptions!E$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="H49" s="12">
+        <f>H42*(G49/G42)*(1+Assumptions!F$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Pizza Hut</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>367</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>433</v>
+      </c>
+      <c r="D50" s="12">
+        <f>D43*(C50/C43)*(1+Assumptions!B$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="E50" s="12">
+        <f>E43*(D50/D43)*(1+Assumptions!C$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="F50" s="12">
+        <f>F43*(E50/E43)*(1+Assumptions!D$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="G50" s="12">
+        <f>G43*(F50/F43)*(1+Assumptions!E$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="H50" s="12">
+        <f>H43*(G50/G43)*(1+Assumptions!F$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Hardee's</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>275</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>330</v>
+      </c>
+      <c r="D51" s="12">
+        <f>D44*(C51/C44)*(1+Assumptions!B$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="E51" s="12">
+        <f>E44*(D51/D44)*(1+Assumptions!C$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="F51" s="12">
+        <f>F44*(E51/E44)*(1+Assumptions!D$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="G51" s="12">
+        <f>G44*(F51/F44)*(1+Assumptions!E$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="H51" s="12">
+        <f>H44*(G51/G44)*(1+Assumptions!F$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Krispy Kreme</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="D52" s="12">
+        <f>D45*(C52/C45)*(1+Assumptions!B$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="E52" s="12">
+        <f>E45*(D52/D45)*(1+Assumptions!C$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="F52" s="12">
+        <f>F45*(E52/E45)*(1+Assumptions!D$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="G52" s="12">
+        <f>G45*(F52/F45)*(1+Assumptions!E$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="H52" s="12">
+        <f>H45*(G52/G45)*(1+Assumptions!F$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Growth, niche and other brands</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>142.7510000000002</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>157.8209999999999</v>
+      </c>
+      <c r="D53" s="12">
+        <f>D46*(C53/C46)*(1+Assumptions!B$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="E53" s="12">
+        <f>E46*(D53/D46)*(1+Assumptions!C$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="F53" s="12">
+        <f>F46*(E53/E46)*(1+Assumptions!D$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="G53" s="12">
+        <f>G46*(F53/F46)*(1+Assumptions!E$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+      <c r="H53" s="12">
+        <f>H46*(G53/G46)*(1+Assumptions!F$30)*(1-0.003203)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Brand build, after eliminations (FY2026 blended with the disclosed half, as above)</t>
+        </is>
+      </c>
+      <c r="D54" s="12">
+        <f>(SUM(D49:D53)*(1-Assumptions!$C$95)+Assumptions!$C$96)/2</f>
+        <v/>
+      </c>
+      <c r="E54" s="12">
+        <f>SUM(E49:E53)*(1-Assumptions!$C$95)</f>
+        <v/>
+      </c>
+      <c r="F54" s="12">
+        <f>SUM(F49:F53)*(1-Assumptions!$C$95)</f>
+        <v/>
+      </c>
+      <c r="G54" s="12">
+        <f>SUM(G49:G53)*(1-Assumptions!$C$95)</f>
+        <v/>
+      </c>
+      <c r="H54" s="12">
+        <f>SUM(H49:H53)*(1-Assumptions!$C$95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Against the geographic build (row 36)</t>
+        </is>
+      </c>
+      <c r="D55" s="13">
+        <f>D54/E36-1</f>
+        <v/>
+      </c>
+      <c r="E55" s="13">
+        <f>E54/F36-1</f>
+        <v/>
+      </c>
+      <c r="F55" s="13">
+        <f>F54/G36-1</f>
+        <v/>
+      </c>
+      <c r="G55" s="13">
+        <f>G54/H36-1</f>
+        <v/>
+      </c>
+      <c r="H55" s="13">
+        <f>H54/I36-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="56" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>The gap is a disclosed-mix effect, stated rather than smoothed: the company's brand-level opening mix is KFC-heavy (40% of openings at about USD 1.3 million of revenue per restaurant) while the geographic mix spreads additions across markets averaging about USD 0.9 million, so the brand build runs about 2% ahead by FY2030. The geographic build is adopted because it ties the audited history exactly; the brand build is the volume-times-price cross-check.</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -7220,7 +7884,7 @@
           <t>Discount factor back to the valuation date</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>DCF!C18</f>
         <v/>
       </c>
@@ -7228,11 +7892,11 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Plus the present value of the FY2026 free cash flow</t>
+          <t>Plus the present value of the FY2026 AND FY2027 free cash flows — a two-year discount makes both years intervening</t>
         </is>
       </c>
       <c r="B9" s="10">
-        <f>DCF!B19</f>
+        <f>DCF!B19+DCF!C19</f>
         <v/>
       </c>
     </row>
@@ -7261,11 +7925,11 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Implied value per share (AED)</t>
+          <t>Implied value per share (AED), rolled to the anchor</t>
         </is>
       </c>
       <c r="B12" s="12">
-        <f>B11/Assumptions!$C$7*Assumptions!$C$6</f>
+        <f>(B11/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -7276,11 +7940,11 @@
         </is>
       </c>
       <c r="C13" s="12">
-        <f>(B5*7*B8+B9+DCF!C33+DCF!C34+DCF!C35+DCF!C36)/Assumptions!$C$7*Assumptions!$C$6</f>
+        <f>((B5*7*B8+B9+DCF!C33+DCF!C34+DCF!C35+DCF!C36)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D13" s="12">
-        <f>(B5*10.5*B8+B9+DCF!C33+DCF!C34+DCF!C35+DCF!C36)/Assumptions!$C$7*Assumptions!$C$6</f>
+        <f>((B5*10.5*B8+B9+DCF!C33+DCF!C34+DCF!C35+DCF!C36)/Assumptions!$C$7*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -7297,7 +7961,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="26">
         <f>(DCF!C56-DCF!C34+DCF!C57)/'Income Statement'!D8</f>
         <v/>
       </c>
@@ -7308,7 +7972,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="26">
         <f>Assumptions!$C$5/Assumptions!$C$6/'Income Statement'!D20</f>
         <v/>
       </c>
@@ -7319,7 +7983,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="26">
         <f>Assumptions!$C$5/Assumptions!$C$6/('Balance Sheet'!D14/Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7356,11 +8020,11 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin (FY2028E)</t>
-        </is>
-      </c>
-      <c r="B23" s="11">
-        <f>DCF!D9</f>
+          <t>Mid-cycle EBITDA margin — the midpoint of the structural and cyclical FY2028 readings</t>
+        </is>
+      </c>
+      <c r="B23" s="13">
+        <f>(DCF!D9+Assumptions!$D$119)/2</f>
         <v/>
       </c>
     </row>
@@ -7389,11 +8053,11 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Normalised EBIT (USD million)</t>
+          <t>Normalised EBIT, after the recurring impairment charge (USD million)</t>
         </is>
       </c>
       <c r="B26" s="12">
-        <f>B24+B25</f>
+        <f>B24+B25-B22*Assumptions!$C$115</f>
         <v/>
       </c>
     </row>
@@ -7404,7 +8068,7 @@
         </is>
       </c>
       <c r="B27" s="12">
-        <f>'Income Statement'!E13-Assumptions!$C$82*'Balance Sheet'!D12</f>
+        <f>'Income Statement'!E13-Assumptions!$C$82*'Balance Sheet'!D12-Assumptions!$C$74*B22</f>
         <v/>
       </c>
     </row>
@@ -7425,7 +8089,7 @@
           <t>Normalised earnings per share (USD)</t>
         </is>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <f>B28/Assumptions!$C$7</f>
         <v/>
       </c>
@@ -7444,11 +8108,11 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Implied value per share (AED)</t>
+          <t>Implied value per share (AED), rolled to the anchor</t>
         </is>
       </c>
       <c r="B31" s="12">
-        <f>B29*B30*Assumptions!$C$6</f>
+        <f>(B29*B30*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -7459,11 +8123,11 @@
         </is>
       </c>
       <c r="C32" s="12">
-        <f>B29*13*Assumptions!$C$6</f>
+        <f>(B29*13*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D32" s="12">
-        <f>B29*21*Assumptions!$C$6</f>
+        <f>(B29*21*DCF!$E$38-Assumptions!$C$118)*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -7480,7 +8144,7 @@
           <t>Book value per share (USD)</t>
         </is>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="27">
         <f>Assumptions!$C$97/Assumptions!$C$7</f>
         <v/>
       </c>
@@ -7524,19 +8188,28 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="26">
         <f>(B36-Assumptions!$C$84)/(B38-Assumptions!$C$84)</f>
+        <v/>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Roll factor from the 30 June book date (38 days)</t>
+        </is>
+      </c>
+      <c r="F39" s="27">
+        <f>(1+DCF!C52)^(38/365)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Implied value per share (AED)</t>
+          <t>Implied value per share (AED), rolled from the book date to the anchor</t>
         </is>
       </c>
       <c r="B40" s="12">
-        <f>B35*B39*Assumptions!$C$6</f>
+        <f>B35*B39*F39*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -7547,11 +8220,11 @@
         </is>
       </c>
       <c r="C41" s="12">
-        <f>B35*((0.34-Assumptions!$C$84)/(B38+0.02-Assumptions!$C$84))*Assumptions!$C$6</f>
+        <f>B35*((0.34-Assumptions!$C$84)/(B38+0.02-Assumptions!$C$84))*F39*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D41" s="12">
-        <f>B35*((0.48-Assumptions!$C$84)/(B38-0.01-Assumptions!$C$84))*Assumptions!$C$6</f>
+        <f>B35*((0.48-Assumptions!$C$84)/(B38-0.01-Assumptions!$C$84))*F39*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -7573,7 +8246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -7660,27 +8333,27 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Cash operating costs</t>
+          <t>Cash operating costs — six escalator classes as shares, staff and delivery as unit builds (headcount x wage; channel share x unit cost)</t>
         </is>
       </c>
       <c r="B6" s="12">
-        <f>-B5*(Assumptions!B$49+Assumptions!B$50+Assumptions!B$51+Assumptions!B$52+Assumptions!B$53+Assumptions!B$54+Assumptions!B$55+Assumptions!B$56+Assumptions!$C$57)</f>
+        <f>-B5*(Assumptions!B$49+Assumptions!B$50+Assumptions!B$53+Assumptions!B$54+Assumptions!B$55+Assumptions!B$56+Assumptions!$C$57)-((Segments!B12+Segments!C12)/2*Assumptions!B$109/1000+Assumptions!$C$112)*Assumptions!$C$110*(1+Assumptions!$C$111)^1-B5*Assumptions!B$113*Assumptions!B$114</f>
         <v/>
       </c>
       <c r="C6" s="12">
-        <f>-C5*(Assumptions!C$49+Assumptions!C$50+Assumptions!C$51+Assumptions!C$52+Assumptions!C$53+Assumptions!C$54+Assumptions!C$55+Assumptions!C$56+Assumptions!$C$57)</f>
+        <f>-C5*(Assumptions!C$49+Assumptions!C$50+Assumptions!C$53+Assumptions!C$54+Assumptions!C$55+Assumptions!C$56+Assumptions!$C$57)-((Segments!C12+Segments!D12)/2*Assumptions!C$109/1000+Assumptions!$C$112)*Assumptions!$C$110*(1+Assumptions!$C$111)^2-C5*Assumptions!C$113*Assumptions!C$114</f>
         <v/>
       </c>
       <c r="D6" s="12">
-        <f>-D5*(Assumptions!D$49+Assumptions!D$50+Assumptions!D$51+Assumptions!D$52+Assumptions!D$53+Assumptions!D$54+Assumptions!D$55+Assumptions!D$56+Assumptions!$C$57)</f>
+        <f>-D5*(Assumptions!D$49+Assumptions!D$50+Assumptions!D$53+Assumptions!D$54+Assumptions!D$55+Assumptions!D$56+Assumptions!$C$57)-((Segments!D12+Segments!E12)/2*Assumptions!D$109/1000+Assumptions!$C$112)*Assumptions!$C$110*(1+Assumptions!$C$111)^3-D5*Assumptions!D$113*Assumptions!D$114</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>-E5*(Assumptions!E$49+Assumptions!E$50+Assumptions!E$51+Assumptions!E$52+Assumptions!E$53+Assumptions!E$54+Assumptions!E$55+Assumptions!E$56+Assumptions!$C$57)</f>
+        <f>-E5*(Assumptions!E$49+Assumptions!E$50+Assumptions!E$53+Assumptions!E$54+Assumptions!E$55+Assumptions!E$56+Assumptions!$C$57)-((Segments!E12+Segments!F12)/2*Assumptions!E$109/1000+Assumptions!$C$112)*Assumptions!$C$110*(1+Assumptions!$C$111)^4-E5*Assumptions!E$113*Assumptions!E$114</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>-F5*(Assumptions!F$49+Assumptions!F$50+Assumptions!F$51+Assumptions!F$52+Assumptions!F$53+Assumptions!F$54+Assumptions!F$55+Assumptions!F$56+Assumptions!$C$57)</f>
+        <f>-F5*(Assumptions!F$49+Assumptions!F$50+Assumptions!F$53+Assumptions!F$54+Assumptions!F$55+Assumptions!F$56+Assumptions!$C$57)-((Segments!F12+Segments!G12)/2*Assumptions!F$109/1000+Assumptions!$C$112)*Assumptions!$C$110*(1+Assumptions!$C$111)^5-F5*Assumptions!F$113*Assumptions!F$114</f>
         <v/>
       </c>
     </row>
@@ -7795,27 +8468,27 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>EBIT, after the recurring impairment charge</t>
         </is>
       </c>
       <c r="B11" s="12">
-        <f>B8+B10</f>
+        <f>B8+B10-B5*Assumptions!$C$115</f>
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>C8+C10</f>
+        <f>C8+C10-C5*Assumptions!$C$115</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>D8+D10</f>
+        <f>D8+D10-D5*Assumptions!$C$115</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>E8+E10</f>
+        <f>E8+E10-E5*Assumptions!$C$115</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>F8+F10</f>
+        <f>F8+F10-F5*Assumptions!$C$115</f>
         <v/>
       </c>
     </row>
@@ -7960,23 +8633,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>$C$46-($C$46-$C$53)*B44</f>
         <v/>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>$C$46-($C$46-$C$53)*C44</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>$C$46-($C$46-$C$53)*D44</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>$C$46-($C$46-$C$53)*E44</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>$C$46-($C$46-$C$53)*F44</f>
         <v/>
       </c>
@@ -7987,23 +8660,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <f>1/(1+B17)</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <f>B18/(1+C17)</f>
         <v/>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <f>C18/(1+D17)</f>
         <v/>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>D18/(1+E17)</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <f>E18/(1+F17)</f>
         <v/>
       </c>
@@ -8078,11 +8751,11 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="C25" s="13">
-        <f>C23/C24</f>
+          <t>Terminal return on incremental capital — the payback-anchored fade</t>
+        </is>
+      </c>
+      <c r="C25" s="11">
+        <f>Assumptions!$C$116</f>
         <v/>
       </c>
     </row>
@@ -8103,7 +8776,7 @@
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>C53</f>
         <v/>
       </c>
@@ -8221,22 +8894,31 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Fair value per share (USD)</t>
-        </is>
-      </c>
-      <c r="C38" s="26">
+          <t>Fair value per share at 31 December 2025 (USD)</t>
+        </is>
+      </c>
+      <c r="C38" s="27">
         <f>C37/Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Anchor roll factor</t>
+        </is>
+      </c>
+      <c r="E38" s="27">
+        <f>(1+C52)^(Assumptions!$C$117/365)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Fair value per share (AED)</t>
+          <t>Fair value per share at the 7 August 2026 anchor (AED) — rolled at the cost of equity, net of the dividend paid in the window</t>
         </is>
       </c>
       <c r="C39" s="12">
-        <f>C38*Assumptions!$C$6</f>
+        <f>(C38*E38-Assumptions!$C$118)*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -8346,7 +9028,7 @@
           <t>Cost of capital, explicit window</t>
         </is>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="28">
         <f>C59*C52+C58*C55</f>
         <v/>
       </c>
@@ -8379,7 +9061,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="28">
         <f>C47-C48</f>
         <v/>
       </c>
@@ -8390,7 +9072,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C50" s="24">
+      <c r="C50" s="25">
         <f>Assumptions!$C$81</f>
         <v/>
       </c>
@@ -8412,7 +9094,7 @@
           <t>Cost of equity</t>
         </is>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="28">
         <f>C49+C50*C51</f>
         <v/>
       </c>
@@ -8423,7 +9105,7 @@
           <t>Cost of capital, terminal</t>
         </is>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="28">
         <f>C59*C61+C58*C62</f>
         <v/>
       </c>
@@ -8445,7 +9127,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="28">
         <f>C54*(1-Assumptions!$B$71)</f>
         <v/>
       </c>
@@ -8457,7 +9139,7 @@
         </is>
       </c>
       <c r="C56" s="12">
-        <f>Assumptions!$C$5/Assumptions!$C$6*Assumptions!$C$8</f>
+        <f>Assumptions!$C$5/Assumptions!$C$6*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
@@ -8511,7 +9193,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="28">
         <f>C60+C50*C51</f>
         <v/>
       </c>
@@ -8522,8 +9204,19 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="28">
         <f>C54*(1-Assumptions!$F$71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Model-implied average return on closing invested capital (the bull reading)</t>
+        </is>
+      </c>
+      <c r="C63" s="13">
+        <f>F12/C24</f>
         <v/>
       </c>
     </row>
@@ -8540,7 +9233,7 @@
           <t>Risk-free rate net of the US sovereign credit-default-swap spread</t>
         </is>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="28">
         <f>C47-Assumptions!$C$79</f>
         <v/>
       </c>
@@ -8562,7 +9255,7 @@
           <t>Cost of equity, credit-default-swap basis</t>
         </is>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="28">
         <f>C65+C50*C66</f>
         <v/>
       </c>
@@ -8573,7 +9266,7 @@
           <t>Cost of capital, credit-default-swap basis</t>
         </is>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="28">
         <f>C59*C67+C58*C55</f>
         <v/>
       </c>
@@ -8582,6 +9275,188 @@
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Both bases are published. The default spread stripped out of the risk-free rate is on the same basis as the premium added back, so sovereign risk is counted once and once only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>THE OTHER READING OF THE OPEN QUESTION — the cyclical margin, computed live</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Cyclical EBITDA margin path</t>
+        </is>
+      </c>
+      <c r="B72" s="11">
+        <f>Assumptions!B$119</f>
+        <v/>
+      </c>
+      <c r="C72" s="11">
+        <f>Assumptions!C$119</f>
+        <v/>
+      </c>
+      <c r="D72" s="11">
+        <f>Assumptions!D$119</f>
+        <v/>
+      </c>
+      <c r="E72" s="11">
+        <f>Assumptions!E$119</f>
+        <v/>
+      </c>
+      <c r="F72" s="11">
+        <f>Assumptions!F$119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA on the cyclical path</t>
+        </is>
+      </c>
+      <c r="B73" s="12">
+        <f>B5*B72</f>
+        <v/>
+      </c>
+      <c r="C73" s="12">
+        <f>C5*C72</f>
+        <v/>
+      </c>
+      <c r="D73" s="12">
+        <f>D5*D72</f>
+        <v/>
+      </c>
+      <c r="E73" s="12">
+        <f>E5*E72</f>
+        <v/>
+      </c>
+      <c r="F73" s="12">
+        <f>F5*F72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>NOPAT on the cyclical path</t>
+        </is>
+      </c>
+      <c r="B74" s="12">
+        <f>(B73+B10-B5*Assumptions!$C$115)*(1-Assumptions!B$71)</f>
+        <v/>
+      </c>
+      <c r="C74" s="12">
+        <f>(C73+C10-C5*Assumptions!$C$115)*(1-Assumptions!C$71)</f>
+        <v/>
+      </c>
+      <c r="D74" s="12">
+        <f>(D73+D10-D5*Assumptions!$C$115)*(1-Assumptions!D$71)</f>
+        <v/>
+      </c>
+      <c r="E74" s="12">
+        <f>(E73+E10-E5*Assumptions!$C$115)*(1-Assumptions!E$71)</f>
+        <v/>
+      </c>
+      <c r="F74" s="12">
+        <f>(F73+F10-F5*Assumptions!$C$115)*(1-Assumptions!F$71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Free cash flow to the firm, cyclical</t>
+        </is>
+      </c>
+      <c r="B75" s="12">
+        <f>B74-B10+B14+B15</f>
+        <v/>
+      </c>
+      <c r="C75" s="12">
+        <f>C74-C10+C14+C15</f>
+        <v/>
+      </c>
+      <c r="D75" s="12">
+        <f>D74-D10+D14+D15</f>
+        <v/>
+      </c>
+      <c r="E75" s="12">
+        <f>E74-E10+E14+E15</f>
+        <v/>
+      </c>
+      <c r="F75" s="12">
+        <f>F74-F10+F14+F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Present value</t>
+        </is>
+      </c>
+      <c r="B76" s="12">
+        <f>B75*B18</f>
+        <v/>
+      </c>
+      <c r="C76" s="12">
+        <f>C75*C18</f>
+        <v/>
+      </c>
+      <c r="D76" s="12">
+        <f>D75*D18</f>
+        <v/>
+      </c>
+      <c r="E76" s="12">
+        <f>E75*E18</f>
+        <v/>
+      </c>
+      <c r="F76" s="12">
+        <f>F75*F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>Terminal value, cyclical</t>
+        </is>
+      </c>
+      <c r="C77" s="12">
+        <f>F74*(1+C22)*(1-C22/C25)/(C27-C22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Equity value, cyclical</t>
+        </is>
+      </c>
+      <c r="C78" s="12">
+        <f>SUM(B76:F76)+C77*F18+C33+C34+C35+C36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Value per share on the cyclical reading (AED), rolled to the anchor</t>
+        </is>
+      </c>
+      <c r="C79" s="12">
+        <f>(C78/Assumptions!$C$7*E38-Assumptions!$C$118)*Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Every cell in this block is a live formula: the cyclical reading shares the revenue, depreciation, capital-expenditure and working-capital lines of the base case and differs only in the margin path, so it can be — and is — computed in the sheet rather than pasted.</t>
         </is>
       </c>
     </row>
@@ -8722,27 +9597,27 @@
       <c r="D6" s="9" t="n">
         <v>-1143.928</v>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8766,27 +9641,27 @@
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H7" s="28" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8909,7 +9784,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>EBIT, before the impairment line beneath</t>
         </is>
       </c>
       <c r="B11" s="12">
@@ -8948,7 +9823,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Impairment losses on non-financial and financial assets</t>
+          <t>Impairment losses — audited history, and the recurring charge in the forecast</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
@@ -8960,30 +9835,25 @@
       <c r="D12" s="9" t="n">
         <v>-5.81</v>
       </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="12">
+        <f>-E5*Assumptions!$C$115</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>-F5*Assumptions!$C$115</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>-G5*Assumptions!$C$115</f>
+        <v/>
+      </c>
+      <c r="H12" s="12">
+        <f>-H5*Assumptions!$C$115</f>
+        <v/>
+      </c>
+      <c r="I12" s="12">
+        <f>-I5*Assumptions!$C$115</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -9077,23 +9947,23 @@
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>E11+E13+E14</f>
+        <f>E11+E12+E13+E14</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>F11+F13+F14</f>
+        <f>F11+F12+F13+F14</f>
         <v/>
       </c>
       <c r="G15" s="12">
-        <f>G11+G13+G14</f>
+        <f>G11+G12+G13+G14</f>
         <v/>
       </c>
       <c r="H15" s="12">
-        <f>H11+H13+H14</f>
+        <f>H11+H12+H13+H14</f>
         <v/>
       </c>
       <c r="I15" s="12">
-        <f>I11+I13+I14</f>
+        <f>I11+I12+I13+I14</f>
         <v/>
       </c>
     </row>
@@ -9187,27 +10057,27 @@
       <c r="D18" s="9" t="n">
         <v>0.6730000000000018</v>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="28" t="inlineStr">
+      <c r="H18" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9258,35 +10128,35 @@
           <t>Earnings per share (USD)</t>
         </is>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>B19/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>C19/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>D19/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>E19/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>F19/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="27">
         <f>G19/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="27">
         <f>H19/Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="27">
         <f>I19/Assumptions!$C$7</f>
         <v/>
       </c>

--- a/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
+++ b/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
@@ -2575,111 +2575,111 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>8.73%</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2.689963203325789</v>
+        <v>2.382012408314553</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>2.860337885054136</v>
+        <v>2.509475706556358</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3.064248697728378</v>
+        <v>2.65875608522669</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3.312848422877485</v>
+        <v>2.836101223653829</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>3.622851685899725</v>
+        <v>3.05039604093331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>9.48%</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>2.362314109361936</v>
+        <v>2.11718304640784</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2.488118720415106</v>
+        <v>2.213762425561353</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.635369723229186</v>
+        <v>2.324888614564916</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2.810182471952523</v>
+        <v>2.454205576947338</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3.021241547941936</v>
+        <v>2.606685240582303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>9.50%</t>
+          <t>10.23%</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>2.100325927119413</v>
+        <v>1.900770309146586</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2.195715870481494</v>
+        <v>1.975525133392451</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.060314379151536</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2.433016097897558</v>
+        <v>2.157371874484469</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2.583368567260923</v>
+        <v>2.269647642457567</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.98%</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1.886105952820147</v>
+        <v>1.720647009368917</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1.959982266853094</v>
+        <v>1.779523046446699</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.043742616089398</v>
+        <v>1.845512419649926</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2.13958005375153</v>
+        <v>1.920040067702721</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.250388237346297</v>
+        <v>2.004938751225483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>11.73%</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1.707719127700286</v>
+        <v>1.568422278821936</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1.765930588738839</v>
+        <v>1.615464943294643</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1.831153911590974</v>
+        <v>1.6676639446737</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1.90478951514285</v>
+        <v>1.725958159365405</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1.988637340851779</v>
+        <v>1.791529128816121</v>
       </c>
     </row>
     <row r="12">
@@ -2719,111 +2719,111 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>8.73%</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>2.596476620793644</v>
+        <v>2.248270096272191</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2.83036265926101</v>
+        <v>2.45351309074944</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3.064248697728378</v>
+        <v>2.65875608522669</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>3.298134736195744</v>
+        <v>2.863999079703938</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.532020774663111</v>
+        <v>3.069242074181188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>9.48%</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>2.22829044897828</v>
+        <v>1.961685449414714</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2.431830086103732</v>
+        <v>2.143287031989815</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2.635369723229186</v>
+        <v>2.324888614564916</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2.838909360354638</v>
+        <v>2.506490197140017</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.04244899748009</v>
+        <v>2.688091779715117</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>9.50%</t>
+          <t>10.23%</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>1.945071282019615</v>
+        <v>1.734611877773381</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2.125246481825268</v>
+        <v>1.897463128462458</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.060314379151536</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2.485596881436576</v>
+        <v>2.223165629840613</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2.665772081242229</v>
+        <v>2.38601688052969</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.98%</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>1.720483475001578</v>
+        <v>1.550282847546133</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1.882113045545488</v>
+        <v>1.697897633598029</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2.043742616089398</v>
+        <v>1.845512419649926</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2.205372186633307</v>
+        <v>1.993127205701823</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2.367001757177217</v>
+        <v>2.140741991753718</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>11.73%</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>1.538054535967304</v>
+        <v>1.397688377414051</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1.684604223779139</v>
+        <v>1.532676161043876</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.831153911590974</v>
+        <v>1.6676639446737</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1.977703599402809</v>
+        <v>1.802651728303525</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2.124253287214644</v>
+        <v>1.93763951193335</v>
       </c>
     </row>
     <row r="20">
@@ -2845,19 +2845,19 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2.15658397818916</v>
+        <v>1.92772200641978</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2.230264896942197</v>
+        <v>1.993364657554657</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.060314379151536</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2.38207632785189</v>
+        <v>2.128590591261212</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2.460251047727809</v>
+        <v>2.19821290477535</v>
       </c>
       <c r="H21" s="12">
         <f>MAX(B21:F21)-MIN(B21:F21)</f>
@@ -2871,19 +2871,19 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>1.945071282019615</v>
+        <v>1.734611877773381</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2.125246481825268</v>
+        <v>1.897463128462458</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.060314379151536</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2.485596881436576</v>
+        <v>2.223165629840613</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2.665772081242229</v>
+        <v>2.38601688052969</v>
       </c>
       <c r="H22" s="12">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>3.064248697728378</v>
+        <v>2.65875608522669</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>2.635369723229186</v>
+        <v>2.324888614564916</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.060314379151536</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2.043742616089398</v>
+        <v>1.845512419649926</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1.831153911590974</v>
+        <v>1.6676639446737</v>
       </c>
       <c r="H23" s="12">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2923,19 +2923,19 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2.100325927119413</v>
+        <v>1.900770309146586</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2.195715870481494</v>
+        <v>1.975525133392451</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.060314379151536</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2.433016097897558</v>
+        <v>2.157371874484469</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2.583368567260923</v>
+        <v>2.269647642457567</v>
       </c>
       <c r="H24" s="12">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -4102,14 +4102,14 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>1.400021011084784</v>
+        <v>1.283974697501694</v>
       </c>
       <c r="C5" s="10">
         <f>DCF!C39</f>
         <v/>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4.29768913036704</v>
+        <v>3.621820779289304</v>
       </c>
       <c r="E5" s="11">
         <f>Assumptions!$C$103</f>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.060314379151536</v>
       </c>
     </row>
     <row r="20">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2.259144982128687</v>
+        <v>2.045002754563084</v>
       </c>
     </row>
     <row r="21">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>0.894</v>
+        <v>1.026</v>
       </c>
     </row>
     <row r="82">

--- a/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
+++ b/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
@@ -2575,111 +2575,111 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>8.20%</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2.689963203325789</v>
+        <v>2.59881486006034</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>2.860337885054136</v>
+        <v>2.75578000679716</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3.064248697728378</v>
+        <v>2.942432946714026</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3.312848422877485</v>
+        <v>3.168230612770638</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>3.622851685899725</v>
+        <v>3.447123723786802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>8.95%</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>2.362314109361936</v>
+        <v>2.29037370929778</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2.488118720415106</v>
+        <v>2.407165738467058</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.635369723229186</v>
+        <v>2.54318052228866</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2.810182471952523</v>
+        <v>2.703700107790479</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3.021241547941936</v>
+        <v>2.896136874934558</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>9.50%</t>
+          <t>9.70%</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>2.100325927119413</v>
+        <v>2.042163821293314</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2.195715870481494</v>
+        <v>2.131257662042504</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.233308017752015</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2.433016097897558</v>
+        <v>2.351445039158722</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2.583368567260923</v>
+        <v>2.489895464546122</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.45%</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1.886105952820147</v>
+        <v>1.838156556980712</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1.959982266853094</v>
+        <v>1.907495924832088</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.043742616089398</v>
+        <v>1.985850313836771</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2.13958005375153</v>
+        <v>2.075162925425672</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.250388237346297</v>
+        <v>2.177978674447895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>11.20%</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1.707719127700286</v>
+        <v>1.667545283529673</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1.765930588738839</v>
+        <v>1.722403267209278</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1.831153911590974</v>
+        <v>1.783697011530936</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1.90478951514285</v>
+        <v>1.852678789731079</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1.988637340851779</v>
+        <v>1.930948299583152</v>
       </c>
     </row>
     <row r="12">
@@ -2719,111 +2719,111 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>8.20%</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>2.596476620793644</v>
+        <v>2.491868709377671</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2.83036265926101</v>
+        <v>2.717150828045848</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3.064248697728378</v>
+        <v>2.942432946714026</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>3.298134736195744</v>
+        <v>3.167715065382204</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.532020774663111</v>
+        <v>3.392997184050382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>8.95%</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>2.22829044897828</v>
+        <v>2.149127751906584</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2.431830086103732</v>
+        <v>2.346154137097622</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2.635369723229186</v>
+        <v>2.54318052228866</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2.838909360354638</v>
+        <v>2.740206907479699</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.04244899748009</v>
+        <v>2.937233292670737</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>9.50%</t>
+          <t>9.70%</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>1.945071282019615</v>
+        <v>1.883150389198714</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2.125246481825268</v>
+        <v>2.058229203475364</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.233308017752015</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2.485596881436576</v>
+        <v>2.408386832028666</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2.665772081242229</v>
+        <v>2.583465646305317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.45%</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>1.720483475001578</v>
+        <v>1.670776226627332</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1.882113045545488</v>
+        <v>1.828313270232051</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2.043742616089398</v>
+        <v>1.985850313836771</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2.205372186633307</v>
+        <v>2.14338735744149</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2.367001757177217</v>
+        <v>2.30092440104621</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>11.20%</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>1.538054535967304</v>
+        <v>1.497309182309147</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1.684604223779139</v>
+        <v>1.640503096920041</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.831153911590974</v>
+        <v>1.783697011530936</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1.977703599402809</v>
+        <v>1.926890926141831</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2.124253287214644</v>
+        <v>2.070084840752726</v>
       </c>
     </row>
     <row r="20">
@@ -2845,19 +2845,19 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2.15658397818916</v>
+        <v>2.089254026961081</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2.230264896942197</v>
+        <v>2.160567950500811</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.233308017752015</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2.38207632785189</v>
+        <v>2.307495465459392</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2.460251047727809</v>
+        <v>2.383151739324826</v>
       </c>
       <c r="H21" s="12">
         <f>MAX(B21:F21)-MIN(B21:F21)</f>
@@ -2871,19 +2871,19 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>1.945071282019615</v>
+        <v>1.883150389198714</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2.125246481825268</v>
+        <v>2.058229203475364</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.233308017752015</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2.485596881436576</v>
+        <v>2.408386832028666</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2.665772081242229</v>
+        <v>2.583465646305317</v>
       </c>
       <c r="H22" s="12">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>3.064248697728378</v>
+        <v>2.942432946714026</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>2.635369723229186</v>
+        <v>2.54318052228866</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.233308017752015</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2.043742616089398</v>
+        <v>1.985850313836771</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1.831153911590974</v>
+        <v>1.783697011530936</v>
       </c>
       <c r="H23" s="12">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2923,19 +2923,19 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2.100325927119413</v>
+        <v>2.042163821293314</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2.195715870481494</v>
+        <v>2.131257662042504</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.233308017752015</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2.433016097897558</v>
+        <v>2.351445039158722</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2.583368567260923</v>
+        <v>2.489895464546122</v>
       </c>
       <c r="H24" s="12">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -4102,14 +4102,14 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>1.400021011084784</v>
+        <v>1.366554912808877</v>
       </c>
       <c r="C5" s="10">
         <f>DCF!C39</f>
         <v/>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4.29768913036704</v>
+        <v>4.090210014429833</v>
       </c>
       <c r="E5" s="11">
         <f>Assumptions!$C$103</f>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2.305421681630923</v>
+        <v>2.233308017752015</v>
       </c>
     </row>
     <row r="20">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>2.259144982128687</v>
+        <v>2.195924444939009</v>
       </c>
     </row>
     <row r="21">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="C81" s="18" t="n">
-        <v>0.894</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="82">

--- a/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
+++ b/engine/amr_study/AMR_Valuation_Model_09082026_public.xlsx
@@ -2324,22 +2324,22 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>1.901524066024989</v>
+        <v>1.93437521871378</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>2.097207816855494</v>
+        <v>2.126692211483889</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>2.229297266835985</v>
+        <v>2.241720731175675</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>2.370441724581929</v>
+        <v>2.363180493089619</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>2.60694021209324</v>
+        <v>2.60461858255926</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>0.49858</v>
+        <v>0.52706</v>
       </c>
     </row>
     <row r="6">
@@ -2349,22 +2349,22 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>1.683373901994757</v>
+        <v>1.729996444524252</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>2.002287203570245</v>
+        <v>2.053123569109837</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2.230701500479637</v>
+        <v>2.252911727725797</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>2.484262361139349</v>
+        <v>2.47124447749607</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>2.960271871748596</v>
+        <v>2.937323506218373</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>0.50078</v>
+        <v>0.53034</v>
       </c>
     </row>
     <row r="8">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>0.15014</v>
+        <v>0.13496</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>0.27504</v>
+        <v>0.26606</v>
       </c>
     </row>
     <row r="10">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>0.128</v>
+        <v>0.09548</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>0.25438</v>
+        <v>0.2041</v>
       </c>
     </row>
     <row r="11">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="B11" s="21" t="n">
-        <v>0.24976</v>
+        <v>0.21854</v>
       </c>
       <c r="C11" s="21" t="n">
-        <v>0.50802</v>
+        <v>0.47326</v>
       </c>
     </row>
     <row r="12">
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="B12" s="21" t="n">
-        <v>0.21174</v>
+        <v>0.15958</v>
       </c>
       <c r="C12" s="21" t="n">
-        <v>0.46714</v>
+        <v>0.38804</v>
       </c>
     </row>
     <row r="14">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>0.03952466367713004</v>
+        <v>0.0368786610878661</v>
       </c>
     </row>
   </sheetData>
@@ -2575,111 +2575,111 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>8.20%</t>
+          <t>8.23%</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2.59881486006034</v>
+        <v>2.584879316195392</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>2.75578000679716</v>
+        <v>2.739886073119715</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2.942432946714026</v>
+        <v>2.924034875636686</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3.168230612770638</v>
+        <v>3.14654915357756</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>3.447123723786802</v>
+        <v>3.421003677599196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>2.29037370929778</v>
+        <v>2.279286923964465</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2.407165738467058</v>
+        <v>2.394752136376857</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.54318052228866</v>
+        <v>2.529121340121986</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2.703700107790479</v>
+        <v>2.687560171116047</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2.896136874934558</v>
+        <v>2.877304929878125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>9.70%</t>
+          <t>9.73%</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>2.042163821293314</v>
+        <v>2.033136297321837</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>2.131257662042504</v>
+        <v>2.121297130123985</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2.233308017752015</v>
+        <v>2.22221792343126</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2.351445039158722</v>
+        <v>2.338966294654063</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>2.489895464546122</v>
+        <v>2.475678838369221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>10.45%</t>
+          <t>10.48%</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1.838156556980712</v>
+        <v>1.830665564080732</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1.907495924832088</v>
+        <v>1.899328892918576</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1.985850313836771</v>
+        <v>1.976880696183387</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2.075162925425672</v>
+        <v>2.065228549022268</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.177978674447895</v>
+        <v>2.166867935987405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>11.20%</t>
+          <t>11.23%</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>1.667545283529673</v>
+        <v>1.661231024700009</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1.722403267209278</v>
+        <v>1.715586953412172</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1.783697011530936</v>
+        <v>1.776294251965406</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1.852678789731079</v>
+        <v>1.844583909258227</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1.930948299583152</v>
+        <v>1.922026996871675</v>
       </c>
     </row>
     <row r="12">
@@ -2719,111 +2719,111 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>8.20%</t>
+          <t>8.23%</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>2.491868709377671</v>
+        <v>2.476073771580925</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2.717150828045848</v>
+        <v>2.700054323608805</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2.942432946714026</v>
+        <v>2.924034875636686</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>3.167715065382204</v>
+        <v>3.148015427664566</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>3.392997184050382</v>
+        <v>3.371995979692446</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>2.149127751906584</v>
+        <v>2.137059296292256</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2.346154137097622</v>
+        <v>2.333090318207121</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2.54318052228866</v>
+        <v>2.529121340121986</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2.740206907479699</v>
+        <v>2.72515236203685</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2.937233292670737</v>
+        <v>2.921183383951714</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>9.70%</t>
+          <t>9.73%</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>1.883150389198714</v>
+        <v>1.873631888631429</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>2.058229203475364</v>
+        <v>2.047924906031343</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2.233308017752015</v>
+        <v>2.22221792343126</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2.408386832028666</v>
+        <v>2.396510940831174</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2.583465646305317</v>
+        <v>2.57080395823109</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>10.45%</t>
+          <t>10.48%</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>1.670776226627332</v>
+        <v>1.66307880904135</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1.828313270232051</v>
+        <v>1.819979752612368</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1.985850313836771</v>
+        <v>1.976880696183387</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2.14338735744149</v>
+        <v>2.133781639754404</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2.30092440104621</v>
+        <v>2.290682583325423</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>11.20%</t>
+          <t>11.23%</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>1.497309182309147</v>
+        <v>1.490957347481012</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1.640503096920041</v>
+        <v>1.633625799723209</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.783697011530936</v>
+        <v>1.776294251965406</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1.926890926141831</v>
+        <v>1.918962704207603</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2.070084840752726</v>
+        <v>2.061631156449801</v>
       </c>
     </row>
     <row r="20">
@@ -2845,19 +2845,19 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2.089254026961081</v>
+        <v>2.078897651507737</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2.160567950500811</v>
+        <v>2.149848521993159</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2.233308017752015</v>
+        <v>2.22221792343126</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2.307495465459392</v>
+        <v>2.29602697648482</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2.383151739324826</v>
+        <v>2.37129700961655</v>
       </c>
       <c r="H21" s="12">
         <f>MAX(B21:F21)-MIN(B21:F21)</f>
@@ -2871,19 +2871,19 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>1.883150389198714</v>
+        <v>1.873631888631429</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2.058229203475364</v>
+        <v>2.047924906031343</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.233308017752015</v>
+        <v>2.22221792343126</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2.408386832028666</v>
+        <v>2.396510940831174</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2.583465646305317</v>
+        <v>2.57080395823109</v>
       </c>
       <c r="H22" s="12">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2897,19 +2897,19 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2.942432946714026</v>
+        <v>2.924034875636686</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>2.54318052228866</v>
+        <v>2.529121340121986</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2.233308017752015</v>
+        <v>2.22221792343126</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1.985850313836771</v>
+        <v>1.976880696183387</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1.783697011530936</v>
+        <v>1.776294251965406</v>
       </c>
       <c r="H23" s="12">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2923,19 +2923,19 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2.042163821293314</v>
+        <v>2.033136297321837</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2.131257662042504</v>
+        <v>2.121297130123985</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.233308017752015</v>
+        <v>2.22221792343126</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2.351445039158722</v>
+        <v>2.338966294654063</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2.489895464546122</v>
+        <v>2.475678838369221</v>
       </c>
       <c r="H24" s="12">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -4102,14 +4102,14 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>1.366554912808877</v>
+        <v>1.3612963353766</v>
       </c>
       <c r="C5" s="10">
         <f>DCF!C39</f>
         <v/>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4.090210014429833</v>
+        <v>4.059369975771861</v>
       </c>
       <c r="E5" s="11">
         <f>Assumptions!$C$103</f>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>2.233308017752015</v>
+        <v>2.22221792343126</v>
       </c>
     </row>
     <row r="20">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="6">
